--- a/Assets/ExcelData/CharacterTable.xlsx
+++ b/Assets/ExcelData/CharacterTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c\Documents\GitHub\OperationKivotos\Assets\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7B2F3D-E074-407A-8EEC-B1ED2067DBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65267EF-DD62-49FC-8981-AFB6C8B84447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33690" yWindow="3300" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character_Stat_Table" sheetId="1" r:id="rId1"/>
@@ -320,32 +320,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>와인레드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>어드마이어</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>크랙 샷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -362,10 +336,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시크릿 타임 + 암기어 건틀릿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>성장치 = (레벨 - 1) × 기본증가량 + ROUND((레벨 - 1)^2 × 가속계수, 0)</t>
   </si>
   <si>
@@ -426,6 +396,14 @@
   </si>
   <si>
     <t>Mat3Rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와인레드&amp;어드마이어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>암기어 건틀릿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -433,7 +411,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,13 +433,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -506,10 +477,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2065,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D8" s="1">
         <v>1006</v>
@@ -2091,7 +2062,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" s="1">
         <v>1007</v>
@@ -2117,7 +2088,7 @@
         <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="1">
         <v>1008</v>
@@ -2143,7 +2114,7 @@
         <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="1">
         <v>1009</v>
@@ -2169,7 +2140,7 @@
         <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" s="1">
         <v>1010</v>
@@ -2195,7 +2166,7 @@
         <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D13" s="1">
         <v>1011</v>
@@ -2247,10 +2218,10 @@
         <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2358,7 +2329,7 @@
         <v>0.04</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2382,7 +2353,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -2427,7 +2398,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -2451,7 +2422,7 @@
         <v>0.104</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -2868,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J2">
         <v>200</v>
@@ -2904,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J3">
         <v>1.1200000000000001</v>
@@ -2922,7 +2893,7 @@
         <v>30000</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ref="D3:D25" si="3">ROUND($J$4*POWER($J$5, A4-2), 0)</f>
+        <f t="shared" ref="D4:D25" si="3">ROUND($J$4*POWER($J$5, A4-2), 0)</f>
         <v>2</v>
       </c>
       <c r="E4" s="1">
@@ -2940,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -2976,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J5">
         <v>1.1000000000000001</v>
@@ -3012,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -3048,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3084,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1.1200000000000001</v>
@@ -3120,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J9">
         <v>18</v>
@@ -3156,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3192,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J11">
         <v>1.1499999999999999</v>
